--- a/output/manduka_products.xlsx
+++ b/output/manduka_products.xlsx
@@ -59,7 +59,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,12 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,12 +445,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>价格(USD)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>月销量</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>相比昨日涨跌额</t>
         </is>
       </c>
     </row>
@@ -458,10 +472,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>58.00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,10 +495,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>62.00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -484,10 +518,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>59.00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -497,10 +541,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>99.00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -510,10 +564,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>280.00</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -523,10 +587,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>230.00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -536,10 +610,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -549,10 +633,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>62.00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -562,10 +656,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>96.00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -575,10 +679,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -588,10 +702,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>114.00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/manduka_products.xlsx
+++ b/output/manduka_products.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品类排行" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品数据" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>商品数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mats</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Props</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mat Carriers</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Towels</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cleaning Products</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -717,6 +858,374 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eQua® Hot Yoga Mat Towel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>46.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GRP® Adapt 1.0 Yoga Mat 5mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GRP® Adapt 2.0 Yoga Mat 5mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>128.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GRP® Adapt Lite 2.1 Yoga Mat 4mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>108.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GRP® Adapt Travel Yoga Mat 1.5mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>66.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Manduka PRO™ Yoga Mat 6mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>144.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Natural Rubber Yoga Mat Restore</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PRO Terra Yoga Mat 6mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>128.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PRO Travel Yoga Mat 2mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>74.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PROlite Terra Yoga Mat 4.7mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PROlite® Long &amp; Wide Yoga Mat 4.7mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>144.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROlite® Yoga Mat 4.7mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>112.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PRO® Long &amp; Wide Yoga Mat 6mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>288.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PRO® Squared Yoga Mat 6mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>350.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Yoga Mat Wash and Refresh</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Yogitoes® Hot Yoga Mat Towel</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>yoga mat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>84.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
